--- a/output/pdf_financials_xlsx/WPM.xlsx
+++ b/output/pdf_financials_xlsx/WPM.xlsx
@@ -4156,37 +4156,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>-28.841</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>-23.197</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>55.301</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>77.00700000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.893</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>160.701</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>47.036</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>66.547</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>-40.091</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>-63.503</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>176.911</v>
       </c>
     </row>
     <row r="93">
@@ -7616,7 +7616,11 @@
           <t>Reserves 19</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -9469,7 +9473,11 @@
           <t>Reserves 23</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -10985,7 +10993,11 @@
           <t>Reserves 20</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -12777,7 +12789,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -13402,7 +13418,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" s="5" t="n">
         <v>-28.841</v>
       </c>

--- a/output/pdf_financials_xlsx/WPM.xlsx
+++ b/output/pdf_financials_xlsx/WPM.xlsx
@@ -5438,10 +5438,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.594</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.505</v>
       </c>
     </row>
     <row r="125">
@@ -5478,10 +5478,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.594</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.505</v>
       </c>
     </row>
     <row r="126">
@@ -14911,7 +14911,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -41181,7 +41185,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">

--- a/output/pdf_financials_xlsx/WPM.xlsx
+++ b/output/pdf_financials_xlsx/WPM.xlsx
@@ -834,28 +834,28 @@
         <v>193.807</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>56.817</v>
+        <v>87.21599999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>295.931</v>
+        <v>484.17</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>345.947</v>
+        <v>125.802</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>658.925</v>
+        <v>760.433</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>565.48</v>
+        <v>675.221</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>573.4400000000001</v>
+        <v>544.568</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>802.587</v>
+        <v>649.893</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1671.648</v>
+        <v>1703.828</v>
       </c>
     </row>
     <row r="12">
@@ -1089,10 +1089,10 @@
         <v>-0.886</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-484.17</v>
+        <v>15.868</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-125.802</v>
+        <v>9.066000000000001</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0.269</v>
@@ -1715,10 +1715,10 @@
         <v>1.559392435362656</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>109.2976479910064</v>
+        <v>3.582078770517153</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>163.2265933153415</v>
+        <v>11.76302678015362</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.03564726960467311</v>
@@ -37780,7 +37780,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">

--- a/output/pdf_financials_xlsx/WPM.xlsx
+++ b/output/pdf_financials_xlsx/WPM.xlsx
@@ -834,28 +834,28 @@
         <v>193.807</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>87.21599999999999</v>
+        <v>73.681</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>484.17</v>
+        <v>244.281</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>125.802</v>
+        <v>125.528</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>760.433</v>
+        <v>754.657</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>675.221</v>
+        <v>511.904</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>544.568</v>
+        <v>505.27</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>649.893</v>
+        <v>620.832</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1703.828</v>
+        <v>1581.641</v>
       </c>
     </row>
     <row r="12">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3.391</v>
+        <v>-3.391</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1.33</v>
+        <v>-1.33</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.886</v>
@@ -1092,7 +1092,7 @@
         <v>15.868</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.066000000000001</v>
+        <v>-9.066000000000001</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0.269</v>
@@ -4763,22 +4763,22 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>0</v>
+        <v>68.151</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0</v>
+        <v>384.922</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>228.68</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>167.561</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -5229,10 +5229,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="3" t="n">
+        <v>-44.494</v>
       </c>
       <c r="J119" s="3" t="n">
         <v>-646.646</v>
@@ -5637,25 +5635,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C129" s="3" t="n">
+        <v>1154.989</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>242.132</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-545.009</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>361.159</v>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
@@ -5886,54 +5876,38 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>431.873</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>431.359</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>584.301</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>538.808</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>477.413</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>501.62</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>845.145</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>743.424</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>751.328</v>
+        <v>750.809</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>1027.331</v>
+        <v>1027.581</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>1905.126</v>
+        <v>1904.981</v>
       </c>
     </row>
   </sheetData>
@@ -14722,7 +14696,11 @@
           <t>Cash generated from operating activities $</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -23151,7 +23129,11 @@
           <t>Impairment charges 11, 14</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -26339,7 +26321,11 @@
           <t>Impairment charges 11</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -28005,7 +27991,11 @@
           <t>Impairment charges 12</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -28900,7 +28890,11 @@
           <t>Cash generated from operating activities $</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E337" s="5" t="n">
         <v>431.873</v>
       </c>
@@ -31128,7 +31122,11 @@
           <t>Impairment charges 11</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E369" s="5" t="n">
         <v>68.151</v>
       </c>
@@ -31262,7 +31260,11 @@
           <t>Deferred income tax recovery 20</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -33920,7 +33922,11 @@
           <t>Deferred income tax recovery 22</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E409" s="5" t="n">
         <v>-1.249</v>
       </c>
@@ -37583,7 +37589,11 @@
           <t>Earnings from operations $</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -39471,7 +39481,11 @@
           <t>Income tax recovery (expense) 24</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -40615,7 +40629,11 @@
           <t>Income tax recovery 24</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -41402,7 +41420,11 @@
           <t>Income tax recovery 20</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
           <t>-</t>
@@ -41471,7 +41493,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
